--- a/results.xlsx
+++ b/results.xlsx
@@ -15,6 +15,14 @@
     <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ConstrainedGoToOpen_1c" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ConstrainedActionObjDoor_1c" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ConstrainedGoToObjDoor_2c" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ConstrainedGoToLocal_2c" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ConstrainedActionObjDoor_2c" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ConstrainedOpenDoor_2c" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ConstrainedPickupDist_2c" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ConstrainedOpenDoorsOrder_2c" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ConstrainedOpenDoorLoc_2c" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ConstrainedGoToOpen_2c" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -916,6 +924,3258 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob LAMAML</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols LAMAML</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>135.32 ± 132.38</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>147.34 ± 130.85</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.22</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>108.37 ± 113.23</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3.63 ± 14.32</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>198.40 ± 109.57</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>42.48 ± 46.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>138.43 ± 133.98</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>134.52 ± 132.16</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>94.04 ± 112.50</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3.91 ± 20.36</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>180.75 ± 113.62</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>39.56 ± 43.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>124.14 ± 124.24</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>150.09 ± 129.12</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>108.68 ± 114.07</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5.79 ± 30.11</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>185.98 ± 115.18</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>35.57 ± 37.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>117.06 ± 123.70</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>138.74 ± 129.09</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>114.71 ± 117.27</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3.48 ± 10.56</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>195.44 ± 109.43</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>32.11 ± 33.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>132.66 ± 120.24</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>121.17 ± 113.95</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>127.27 ± 116.40</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2.00 ± 3.02</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>234.61 ± 90.36</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>37.04 ± 34.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>134.31 ± 124.38</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>138.50 ± 127.55</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>134.56 ± 117.67</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2.63 ± 6.96</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>238.35 ± 95.86</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>39.79 ± 36.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>130.32 ± 126.80</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.09</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>138.39 ± 127.61</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.14</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>114.61 ± 115.97</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>3.57 ± 16.85</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>205.59 ± 108.46</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>37.76 ± 38.99</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob LAMAML</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols LAMAML</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>388.59 ± 426.32</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.55 ± 6.09</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>654.56 ± 445.99</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>549.81 ± 460.41</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.52 ± 2.00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>671.52 ± 413.97</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>70.65 ± 71.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>388.59 ± 426.32</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>1.55 ± 6.09</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>654.56 ± 445.99</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>549.81 ± 460.41</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>0.52 ± 2.00</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>671.52 ± 413.97</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>70.65 ± 71.29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob LAMAML</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols LAMAML</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>292.40 ± 328.70</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3.55 ± 9.82</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>278.57 ± 323.63</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1.33 ± 4.74</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>397.10 ± 345.70</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>9.72 ± 12.55</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>611.27 ± 259.84</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>73.77 ± 64.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>235.32 ± 282.42</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.97 ± 2.22</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>246.08 ± 286.95</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.33 ± 1.04</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>495.93 ± 347.89</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14.65 ± 26.93</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>602.00 ± 286.73</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>55.10 ± 52.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>287.30 ± 293.23</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.70 ± 5.27</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>316.03 ± 307.24</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.38 ± 1.61</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>536.77 ± 323.84</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>15.55 ± 21.54</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>595.92 ± 284.71</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>46.05 ± 44.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>297.57 ± 292.57</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.38 ± 1.24</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>293.53 ± 272.62</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.12 ± 0.55</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>484.78 ± 336.65</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>11.18 ± 21.08</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>710.03 ± 198.14</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>46.28 ± 32.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>317.93 ± 278.30</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.70 ± 7.74</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>353.72 ± 279.83</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.28</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>500.15 ± 306.78</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>7.90 ± 10.94</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>671.05 ± 219.21</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>36.03 ± 36.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>286.10 ± 296.85</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>1.66 ± 6.27</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>297.59 ± 296.86</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>0.44 ± 2.35</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>482.95 ± 335.74</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>11.80 ± 19.77</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>638.05 ± 256.19</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>51.45 ± 49.22</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob LAMAML</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols LAMAML</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>256.41 ± 201.72</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6.50 ± 18.79</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>323.17 ± 195.62</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11.44 ± 36.86</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>244.56 ± 192.41</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.93 ± 2.71</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>413.87 ± 158.73</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>63.08 ± 58.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>307.28 ± 206.76</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12.33 ± 31.86</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>325.05 ± 207.23</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11.90 ± 38.08</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>333.32 ± 205.97</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2.08 ± 5.21</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>413.19 ± 169.51</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>62.00 ± 57.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>240.09 ± 198.37</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5.66 ± 9.85</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>213.97 ± 203.08</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4.20 ± 7.47</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>259.47 ± 187.22</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.83 ± 1.75</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>423.76 ± 138.42</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>43.03 ± 40.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>297.79 ± 209.61</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5.83 ± 8.43</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>293.79 ± 205.80</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10.49 ± 35.17</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>294.98 ± 202.56</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.44 ± 3.67</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>409.70 ± 167.31</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>53.21 ± 48.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>252.16 ± 201.51</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4.93 ± 6.65</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>302.04 ± 208.50</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4.10 ± 6.07</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>294.11 ± 191.66</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.98 ± 2.43</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>433.94 ± 138.53</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>33.83 ± 32.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>328.50 ± 195.41</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5.37 ± 11.83</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>369.76 ± 185.84</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5.20 ± 7.34</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>341.14 ± 184.65</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.98 ± 1.96</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>436.41 ± 141.71</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>32.82 ± 30.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>280.37 ± 204.88</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>6.77 ± 17.12</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>304.63 ± 206.62</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>7.89 ± 26.66</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>294.60 ± 197.38</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>1.21 ± 3.21</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>421.81 ± 153.30</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>47.99 ± 47.64</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob LAMAML</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols LAMAML</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>318.77 ± 464.13</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.10 ± 0.48</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>330.53 ± 455.63</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>372.74 ± 449.95</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5.77 ± 12.70</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>650.79 ± 447.73</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>97.08 ± 95.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>308.64 ± 417.60</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>327.48 ± 443.80</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>393.93 ± 438.99</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4.24 ± 10.19</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>715.26 ± 447.85</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>94.35 ± 80.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>300.96 ± 357.58</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>273.17 ± 350.23</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.50</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>367.29 ± 384.86</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.85 ± 4.62</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>837.33 ± 433.88</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>84.05 ± 71.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>339.49 ± 363.49</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.07 ± 0.51</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>395.28 ± 435.23</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>495.68 ± 452.84</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2.14 ± 4.97</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>824.99 ± 414.38</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>69.75 ± 58.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>257.84 ± 304.03</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>394.06 ± 421.60</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>457.73 ± 431.51</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.63 ± 1.40</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>908.77 ± 413.53</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>51.86 ± 46.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>305.14 ± 386.23</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.32</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>344.10 ± 425.44</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.24</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>417.47 ± 435.28</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>2.93 ± 8.12</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>787.43 ± 441.47</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>79.42 ± 74.50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob LAMAML</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols LAMAML</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>526.44 ± 372.97</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8.79 ± 50.53</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>435.05 ± 377.33</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>17.10 ± 58.93</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>318.05 ± 355.24</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4.53 ± 9.93</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>556.68 ± 307.03</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>72.80 ± 75.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>493.63 ± 372.82</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8.37 ± 17.37</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>479.22 ± 373.13</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10.51 ± 20.76</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>270.00 ± 321.11</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2.36 ± 7.20</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>528.12 ± 297.11</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>52.59 ± 44.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>452.87 ± 379.60</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>9.20 ± 19.73</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>453.06 ± 372.64</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9.79 ± 20.12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>339.38 ± 324.03</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2.13 ± 6.11</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>592.62 ± 280.53</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>50.33 ± 46.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>440.52 ± 377.45</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6.13 ± 15.52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>430.19 ± 368.86</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8.72 ± 29.84</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>279.35 ± 316.31</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.09 ± 3.14</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>582.71 ± 283.79</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>43.88 ± 45.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>449.37 ± 380.64</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10.21 ± 35.51</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>412.59 ± 371.02</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5.01 ± 17.08</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>335.45 ± 321.98</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.94 ± 2.94</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>616.09 ± 273.49</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>31.55 ± 40.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>472.57 ± 378.11</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>8.54 ± 30.84</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>442.02 ± 373.29</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>10.23 ± 33.37</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>308.45 ± 329.28</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>2.21 ± 6.55</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>575.24 ± 290.23</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>50.23 ± 53.77</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob LAMAML</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols LAMAML</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>539.35 ± 437.16</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>12.13 ± 45.11</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>519.29 ± 425.77</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>26.79 ± 73.99</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>489.38 ± 426.06</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>17.86 ± 54.56</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>603.31 ± 396.23</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>38.25 ± 83.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>555.66 ± 426.28</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12.30 ± 30.90</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>523.50 ± 443.34</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>27.59 ± 115.99</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>496.68 ± 432.37</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>44.42 ± 162.33</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>647.50 ± 404.81</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>39.95 ± 86.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>687.05 ± 416.69</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>16.65 ± 45.48</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>697.88 ± 414.20</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>32.87 ± 71.73</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>584.48 ± 447.54</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>29.90 ± 66.27</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>781.25 ± 365.14</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>44.05 ± 75.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>678.31 ± 430.05</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>12.25 ± 47.69</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>680.26 ± 435.23</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>39.32 ± 126.28</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>669.14 ± 405.87</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>34.02 ± 91.96</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>774.77 ± 352.56</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>30.79 ± 65.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>615.09 ± 432.97</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>13.33 ± 42.86</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>605.23 ± 437.92</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>31.64 ± 100.15</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>559.92 ± 434.46</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>31.55 ± 103.13</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>701.71 ± 388.19</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>38.26 ± 78.38</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4436,4 +7696,502 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob LAMAML</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols LAMAML</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>111.39 ± 103.79</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>94.96 ± 104.55</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>91.25 ± 97.84</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>212.12 ± 106.72</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>24.08 ± 22.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>116.78 ± 111.15</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>93.15 ± 106.10</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>95.11 ± 100.60</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.35 ± 1.98</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>219.37 ± 107.97</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>24.16 ± 25.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>110.55 ± 109.22</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>103.43 ± 105.04</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>104.87 ± 102.90</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.25 ± 1.40</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>213.25 ± 105.72</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>23.19 ± 24.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>93.21 ± 106.87</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>102.25 ± 99.72</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>108.39 ± 95.36</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.08 ± 0.34</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>229.93 ± 104.34</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>26.09 ± 28.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>108.28 ± 111.44</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>110.92 ± 108.48</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>110.49 ± 105.89</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.11 ± 0.34</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>217.15 ± 108.52</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>28.11 ± 32.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>108.04 ± 108.82</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>100.94 ± 105.01</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>102.02 ± 100.87</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>0.16 ± 1.11</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>218.36 ± 106.85</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>25.13 ± 27.32</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>